--- a/docs/StructureDefinition-DIPSDocumentReferenceEventTime.xlsx
+++ b/docs/StructureDefinition-DIPSDocumentReferenceEventTime.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T19:41:15+00:00</t>
+    <t>2026-09-29T03:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSDocumentReferenceEventTime.xlsx
+++ b/docs/StructureDefinition-DIPSDocumentReferenceEventTime.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T03:57:01+00:00</t>
+    <t>2026-09-29T04:18:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
